--- a/src/experiments/results/demand_based_model.xlsx
+++ b/src/experiments/results/demand_based_model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,6 +461,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>coordinate_node</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>type</t>
         </is>
       </c>
@@ -490,11 +495,8 @@
       <c r="F2" t="n">
         <v>7.041318</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -521,11 +523,8 @@
       <c r="F3" t="n">
         <v>6.95997</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -552,11 +551,8 @@
       <c r="F4" t="n">
         <v>6.99259</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,11 +579,8 @@
       <c r="F5" t="n">
         <v>6.994143</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -614,11 +607,8 @@
       <c r="F6" t="n">
         <v>6.963554</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -645,11 +635,8 @@
       <c r="F7" t="n">
         <v>7.011476</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -676,11 +663,8 @@
       <c r="F8" t="n">
         <v>7.009256</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -707,11 +691,8 @@
       <c r="F9" t="n">
         <v>7.003564</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -738,11 +719,8 @@
       <c r="F10" t="n">
         <v>7.048336</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -769,11 +747,8 @@
       <c r="F11" t="n">
         <v>6.870121</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -800,11 +775,8 @@
       <c r="F12" t="n">
         <v>7.054714</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -831,11 +803,8 @@
       <c r="F13" t="n">
         <v>6.852541</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -862,11 +831,8 @@
       <c r="F14" t="n">
         <v>6.631578</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -893,11 +859,8 @@
       <c r="F15" t="n">
         <v>6.596771</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -924,11 +887,8 @@
       <c r="F16" t="n">
         <v>6.88934</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -955,11 +915,8 @@
       <c r="F17" t="n">
         <v>7.183021</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -986,11 +943,8 @@
       <c r="F18" t="n">
         <v>7.227015</v>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1017,11 +971,8 @@
       <c r="F19" t="n">
         <v>7.185803</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1048,11 +999,8 @@
       <c r="F20" t="n">
         <v>6.88979</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1079,11 +1027,8 @@
       <c r="F21" t="n">
         <v>6.909871</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1110,11 +1055,8 @@
       <c r="F22" t="n">
         <v>6.744279</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1141,11 +1083,8 @@
       <c r="F23" t="n">
         <v>6.756487</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1172,11 +1111,8 @@
       <c r="F24" t="n">
         <v>6.68297</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1203,11 +1139,8 @@
       <c r="F25" t="n">
         <v>6.714977</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1234,11 +1167,8 @@
       <c r="F26" t="n">
         <v>7.351777</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1265,11 +1195,8 @@
       <c r="F27" t="n">
         <v>7.113175</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1296,11 +1223,8 @@
       <c r="F28" t="n">
         <v>7.178492</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1327,34 +1251,36 @@
       <c r="F29" t="n">
         <v>7.186793</v>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>POINT (6.897283728426022 49.26103180854946)</t>
+          <t>POINT (7.053740447534846 49.36988515985408)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10041</v>
+        <v>10043</v>
       </c>
       <c r="C30" t="n">
-        <v>277631240</v>
+        <v>274802949</v>
       </c>
       <c r="D30" t="n">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="E30" t="n">
-        <v>49.26103180854946</v>
+        <v>49.3704692</v>
       </c>
       <c r="F30" t="n">
-        <v>6.897283728426022</v>
+        <v>7.054294</v>
       </c>
       <c r="G30" t="inlineStr">
+        <is>
+          <t>POINT (7.054294 49.3704692)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>predicted</t>
         </is>
@@ -1363,25 +1289,30 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>POINT (7.0726373981436605 49.308497999106905)</t>
+          <t>POINT (7.042880700057395 49.46402636436459)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10041</v>
+        <v>10043</v>
       </c>
       <c r="C31" t="n">
-        <v>6446594345</v>
+        <v>387699574</v>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="E31" t="n">
-        <v>49.3084979991069</v>
+        <v>49.4560808</v>
       </c>
       <c r="F31" t="n">
-        <v>7.072637398143661</v>
+        <v>7.0469057</v>
       </c>
       <c r="G31" t="inlineStr">
+        <is>
+          <t>POINT (7.0469057 49.4560808)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>predicted</t>
         </is>
@@ -1390,25 +1321,30 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>POINT (6.972482045520391 49.32001446257045)</t>
+          <t>POINT (7.089016824188722 49.454222635636455)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>10043</v>
       </c>
       <c r="C32" t="n">
-        <v>1520262802</v>
+        <v>293461246</v>
       </c>
       <c r="D32" t="n">
         <v>20</v>
       </c>
       <c r="E32" t="n">
-        <v>49.32001446257045</v>
+        <v>49.4544287</v>
       </c>
       <c r="F32" t="n">
-        <v>6.972482045520391</v>
+        <v>7.0931871</v>
       </c>
       <c r="G32" t="inlineStr">
+        <is>
+          <t>POINT (7.0931871 49.4544287)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>predicted</t>
         </is>
@@ -1417,25 +1353,30 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>POINT (7.067951977715673 49.35462857787192)</t>
+          <t>POINT (7.2539510560345635 49.41065559607046)</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>10043</v>
       </c>
       <c r="C33" t="n">
-        <v>852826859</v>
+        <v>292315393</v>
       </c>
       <c r="D33" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E33" t="n">
-        <v>49.35462857787192</v>
+        <v>49.4132694</v>
       </c>
       <c r="F33" t="n">
-        <v>7.067951977715673</v>
+        <v>7.2593963</v>
       </c>
       <c r="G33" t="inlineStr">
+        <is>
+          <t>POINT (7.2593963 49.4132694)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>predicted</t>
         </is>
@@ -1444,25 +1385,30 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>POINT (7.168241721227014 49.41688549006543)</t>
+          <t>POINT (7.251562436868623 49.48378432620258)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>10043</v>
       </c>
       <c r="C34" t="n">
-        <v>432636403</v>
+        <v>2312898461</v>
       </c>
       <c r="D34" t="n">
         <v>20</v>
       </c>
       <c r="E34" t="n">
-        <v>49.41688549006543</v>
+        <v>49.4845772</v>
       </c>
       <c r="F34" t="n">
-        <v>7.168241721227014</v>
+        <v>7.2508862</v>
       </c>
       <c r="G34" t="inlineStr">
+        <is>
+          <t>POINT (7.2508862 49.4845772)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>predicted</t>
         </is>
@@ -1471,25 +1417,30 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>POINT (7.014308245977545 49.55378200721683)</t>
+          <t>POINT (6.955047148038068 49.4893808155207)</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>10046</v>
       </c>
       <c r="C35" t="n">
-        <v>5028874262</v>
+        <v>677494934</v>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="E35" t="n">
-        <v>49.55378200721683</v>
+        <v>49.4905338</v>
       </c>
       <c r="F35" t="n">
-        <v>7.014308245977545</v>
+        <v>6.9451934</v>
       </c>
       <c r="G35" t="inlineStr">
+        <is>
+          <t>POINT (6.9451934 49.4905338)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>predicted</t>
         </is>
@@ -1498,25 +1449,30 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>POINT (7.039140903203022 49.520419955976486)</t>
+          <t>POINT (7.040245200614386 49.50964870909265)</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>10046</v>
       </c>
       <c r="C36" t="n">
-        <v>276835128</v>
+        <v>401565186</v>
       </c>
       <c r="D36" t="n">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="E36" t="n">
-        <v>49.52041995597649</v>
+        <v>49.5048732</v>
       </c>
       <c r="F36" t="n">
-        <v>7.039140903203022</v>
+        <v>7.0347213</v>
       </c>
       <c r="G36" t="inlineStr">
+        <is>
+          <t>POINT (7.0347213 49.5048732)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>predicted</t>
         </is>
@@ -1525,25 +1481,30 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>POINT (7.0628196480373395 49.53958706391159)</t>
+          <t>POINT (7.0858126637549095 49.55566814444184)</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>10046</v>
       </c>
       <c r="C37" t="n">
-        <v>590043423</v>
+        <v>712062396</v>
       </c>
       <c r="D37" t="n">
         <v>20</v>
       </c>
       <c r="E37" t="n">
-        <v>49.53958706391159</v>
+        <v>49.5605616</v>
       </c>
       <c r="F37" t="n">
-        <v>7.06281964803734</v>
+        <v>7.0840487</v>
       </c>
       <c r="G37" t="inlineStr">
+        <is>
+          <t>POINT (7.0840487 49.5605616)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>predicted</t>
         </is>
@@ -1552,25 +1513,30 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>POINT (7.00439946897283 49.508377007417735)</t>
+          <t>POINT (7.155779242004266 49.530505699435025)</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>10046</v>
       </c>
       <c r="C38" t="n">
-        <v>1303476026</v>
+        <v>1586177900</v>
       </c>
       <c r="D38" t="n">
         <v>20</v>
       </c>
       <c r="E38" t="n">
-        <v>49.50837700741774</v>
+        <v>49.5319604</v>
       </c>
       <c r="F38" t="n">
-        <v>7.00439946897283</v>
+        <v>7.1633437</v>
       </c>
       <c r="G38" t="inlineStr">
+        <is>
+          <t>POINT (7.1633437 49.5319604)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>predicted</t>
         </is>
@@ -1579,25 +1545,30 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>POINT (7.257106525394624 49.5413431797397)</t>
+          <t>POINT (7.215580179348846 49.53343482539624)</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>10046</v>
       </c>
       <c r="C39" t="n">
-        <v>2235027806</v>
+        <v>382271153</v>
       </c>
       <c r="D39" t="n">
         <v>20</v>
       </c>
       <c r="E39" t="n">
-        <v>49.5413431797397</v>
+        <v>49.5315075</v>
       </c>
       <c r="F39" t="n">
-        <v>7.257106525394624</v>
+        <v>7.2157147</v>
       </c>
       <c r="G39" t="inlineStr">
+        <is>
+          <t>POINT (7.2157147 49.5315075)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>predicted</t>
         </is>
